--- a/Nuevos DeepWins/Problem5_SineHighFreq/Res/Comparativa_9_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem5_SineHighFreq/Res/Comparativa_9_Neuronas.xlsx
@@ -581,42 +581,42 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.248882</v>
+        <v>0.245467</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1790732718</v>
+        <v>1790732668</v>
       </c>
       <c r="E2" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
         <v>200000</v>
       </c>
       <c r="G2" t="n">
-        <v>0.522103</v>
+        <v>0.5318349999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5455680000000001</v>
+        <v>0.5318349999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.533578</v>
+        <v>0.5318349999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>0.250777</v>
+        <v>0.251454</v>
       </c>
       <c r="K2" t="n">
-        <v>0.524017</v>
+        <v>0.577465</v>
       </c>
       <c r="L2" t="n">
-        <v>0.535714</v>
+        <v>0.549107</v>
       </c>
       <c r="M2" t="n">
-        <v>0.529801</v>
+        <v>0.562929</v>
       </c>
       <c r="N2" t="n">
         <v>0.2</v>
@@ -652,23 +652,23 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_5.txt</t>
+          <t>_2_9_1_1790732668_5.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z2" t="n">
         <v>9</v>
       </c>
       <c r="AA2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -682,7 +682,7 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.249119</v>
+        <v>0.2491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -699,16 +699,16 @@
         <v>200000</v>
       </c>
       <c r="G3" t="n">
-        <v>0.521793</v>
+        <v>0.523212</v>
       </c>
       <c r="H3" t="n">
-        <v>0.523096</v>
+        <v>0.520599</v>
       </c>
       <c r="I3" t="n">
-        <v>0.522444</v>
+        <v>0.521902</v>
       </c>
       <c r="J3" t="n">
-        <v>0.251142</v>
+        <v>0.250941</v>
       </c>
       <c r="K3" t="n">
         <v>0.5183489999999999</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_2.txt</t>
+          <t>_2_3_3_3_1_1790732718_14.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -783,42 +783,42 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.249008</v>
+        <v>0.243625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1790732718</v>
+        <v>1790732668</v>
       </c>
       <c r="E4" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
         <v>200000</v>
       </c>
       <c r="G4" t="n">
-        <v>0.522811</v>
+        <v>0.544432</v>
       </c>
       <c r="H4" t="n">
-        <v>0.529338</v>
+        <v>0.604245</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5260550000000001</v>
+        <v>0.572781</v>
       </c>
       <c r="J4" t="n">
-        <v>0.250945</v>
+        <v>0.251479</v>
       </c>
       <c r="K4" t="n">
-        <v>0.522523</v>
+        <v>0.582609</v>
       </c>
       <c r="L4" t="n">
-        <v>0.517857</v>
+        <v>0.598214</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5201789999999999</v>
+        <v>0.5903080000000001</v>
       </c>
       <c r="N4" t="n">
         <v>0.2</v>
@@ -854,23 +854,23 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_11.txt</t>
+          <t>_2_9_1_1790732668_18.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z4" t="n">
         <v>9</v>
       </c>
       <c r="AA4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -884,42 +884,42 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.248937</v>
+        <v>0.244084</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1790732718</v>
+        <v>1790732668</v>
       </c>
       <c r="E5" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
         <v>200000</v>
       </c>
       <c r="G5" t="n">
-        <v>0.52381</v>
+        <v>0.545455</v>
       </c>
       <c r="H5" t="n">
-        <v>0.521848</v>
+        <v>0.606742</v>
       </c>
       <c r="I5" t="n">
-        <v>0.522827</v>
+        <v>0.574468</v>
       </c>
       <c r="J5" t="n">
-        <v>0.251048</v>
+        <v>0.251388</v>
       </c>
       <c r="K5" t="n">
-        <v>0.520362</v>
+        <v>0.5911110000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.513393</v>
+        <v>0.59375</v>
       </c>
       <c r="M5" t="n">
-        <v>0.516854</v>
+        <v>0.592428</v>
       </c>
       <c r="N5" t="n">
         <v>0.2</v>
@@ -955,23 +955,23 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_1.txt</t>
+          <t>_2_9_1_1790732668_14.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z5" t="n">
         <v>9</v>
       </c>
       <c r="AA5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -985,42 +985,42 @@
         <v>0.1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.243625</v>
+        <v>0.248937</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1790732668</v>
+        <v>1790732718</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="F6" t="n">
         <v>200000</v>
       </c>
       <c r="G6" t="n">
-        <v>0.544432</v>
+        <v>0.52381</v>
       </c>
       <c r="H6" t="n">
-        <v>0.604245</v>
+        <v>0.521848</v>
       </c>
       <c r="I6" t="n">
-        <v>0.572781</v>
+        <v>0.522827</v>
       </c>
       <c r="J6" t="n">
-        <v>0.251479</v>
+        <v>0.251048</v>
       </c>
       <c r="K6" t="n">
-        <v>0.582609</v>
+        <v>0.520362</v>
       </c>
       <c r="L6" t="n">
-        <v>0.598214</v>
+        <v>0.513393</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5903080000000001</v>
+        <v>0.516854</v>
       </c>
       <c r="N6" t="n">
         <v>0.2</v>
@@ -1056,23 +1056,23 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_18.txt</t>
+          <t>_2_3_3_3_1_1790732718_1.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z6" t="n">
         <v>9</v>
       </c>
       <c r="AA6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1086,7 +1086,7 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.245094</v>
+        <v>0.245522</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1103,25 +1103,25 @@
         <v>200000</v>
       </c>
       <c r="G7" t="n">
-        <v>0.546498</v>
+        <v>0.553653</v>
       </c>
       <c r="H7" t="n">
-        <v>0.594257</v>
+        <v>0.6054929999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5693780000000001</v>
+        <v>0.578414</v>
       </c>
       <c r="J7" t="n">
-        <v>0.251513</v>
+        <v>0.252012</v>
       </c>
       <c r="K7" t="n">
-        <v>0.590909</v>
+        <v>0.591928</v>
       </c>
       <c r="L7" t="n">
-        <v>0.580357</v>
+        <v>0.589286</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5855860000000001</v>
+        <v>0.590604</v>
       </c>
       <c r="N7" t="n">
         <v>0.2</v>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_3.txt</t>
+          <t>_2_9_1_1790732668_6.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1187,7 +1187,7 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.245524</v>
+        <v>0.245026</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1204,25 +1204,25 @@
         <v>200000</v>
       </c>
       <c r="G8" t="n">
-        <v>0.559955</v>
+        <v>0.551208</v>
       </c>
       <c r="H8" t="n">
-        <v>0.617977</v>
+        <v>0.598002</v>
       </c>
       <c r="I8" t="n">
-        <v>0.587537</v>
+        <v>0.573653</v>
       </c>
       <c r="J8" t="n">
-        <v>0.251892</v>
+        <v>0.251791</v>
       </c>
       <c r="K8" t="n">
-        <v>0.578261</v>
+        <v>0.587156</v>
       </c>
       <c r="L8" t="n">
-        <v>0.59375</v>
+        <v>0.571429</v>
       </c>
       <c r="M8" t="n">
-        <v>0.585903</v>
+        <v>0.5791849999999999</v>
       </c>
       <c r="N8" t="n">
         <v>0.2</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_8.txt</t>
+          <t>_2_9_1_1790732668_12.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1288,42 +1288,42 @@
         <v>0.1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.245467</v>
+        <v>0.249008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1790732668</v>
+        <v>1790732718</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="F9" t="n">
         <v>200000</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5318349999999999</v>
+        <v>0.522811</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5318349999999999</v>
+        <v>0.529338</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5318349999999999</v>
+        <v>0.5260550000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.251454</v>
+        <v>0.250945</v>
       </c>
       <c r="K9" t="n">
-        <v>0.577465</v>
+        <v>0.522523</v>
       </c>
       <c r="L9" t="n">
-        <v>0.549107</v>
+        <v>0.517857</v>
       </c>
       <c r="M9" t="n">
-        <v>0.562929</v>
+        <v>0.5201789999999999</v>
       </c>
       <c r="N9" t="n">
         <v>0.2</v>
@@ -1359,23 +1359,23 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_5.txt</t>
+          <t>_2_3_3_3_1_1790732718_11.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z9" t="n">
         <v>9</v>
       </c>
       <c r="AA9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1389,7 +1389,7 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.243187</v>
+        <v>0.240946</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
         <v>200000</v>
       </c>
       <c r="G10" t="n">
-        <v>0.54535</v>
+        <v>0.557032</v>
       </c>
       <c r="H10" t="n">
-        <v>0.593009</v>
+        <v>0.627965</v>
       </c>
       <c r="I10" t="n">
-        <v>0.568182</v>
+        <v>0.590376</v>
       </c>
       <c r="J10" t="n">
-        <v>0.252278</v>
+        <v>0.250354</v>
       </c>
       <c r="K10" t="n">
-        <v>0.579186</v>
+        <v>0.59276</v>
       </c>
       <c r="L10" t="n">
-        <v>0.571429</v>
+        <v>0.584821</v>
       </c>
       <c r="M10" t="n">
-        <v>0.575281</v>
+        <v>0.588764</v>
       </c>
       <c r="N10" t="n">
         <v>0.2</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_17.txt</t>
+          <t>_2_9_1_1790732668_16.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1490,7 +1490,7 @@
         <v>0.1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.246358</v>
+        <v>0.245524</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1507,25 +1507,25 @@
         <v>200000</v>
       </c>
       <c r="G11" t="n">
-        <v>0.534739</v>
+        <v>0.559955</v>
       </c>
       <c r="H11" t="n">
-        <v>0.538077</v>
+        <v>0.617977</v>
       </c>
       <c r="I11" t="n">
-        <v>0.536403</v>
+        <v>0.587537</v>
       </c>
       <c r="J11" t="n">
-        <v>0.251238</v>
+        <v>0.251892</v>
       </c>
       <c r="K11" t="n">
-        <v>0.577982</v>
+        <v>0.578261</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5625</v>
+        <v>0.59375</v>
       </c>
       <c r="M11" t="n">
-        <v>0.570136</v>
+        <v>0.585903</v>
       </c>
       <c r="N11" t="n">
         <v>0.2</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_11.txt</t>
+          <t>_2_9_1_1790732668_8.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1591,42 +1591,42 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.241644</v>
+        <v>0.248869</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1790732668</v>
+        <v>1790732718</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="F12" t="n">
         <v>200000</v>
       </c>
       <c r="G12" t="n">
-        <v>0.572549</v>
+        <v>0.524089</v>
       </c>
       <c r="H12" t="n">
-        <v>0.546816</v>
+        <v>0.556804</v>
       </c>
       <c r="I12" t="n">
-        <v>0.559387</v>
+        <v>0.539952</v>
       </c>
       <c r="J12" t="n">
-        <v>0.251533</v>
+        <v>0.250745</v>
       </c>
       <c r="K12" t="n">
-        <v>0.564767</v>
+        <v>0.528139</v>
       </c>
       <c r="L12" t="n">
-        <v>0.486607</v>
+        <v>0.544643</v>
       </c>
       <c r="M12" t="n">
-        <v>0.522782</v>
+        <v>0.536264</v>
       </c>
       <c r="N12" t="n">
         <v>0.2</v>
@@ -1662,23 +1662,23 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_7.txt</t>
+          <t>_2_3_3_3_1_1790732718_3.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z12" t="n">
         <v>9</v>
       </c>
       <c r="AA12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1692,7 +1692,7 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.248893</v>
+        <v>0.248981</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1709,25 +1709,25 @@
         <v>200000</v>
       </c>
       <c r="G13" t="n">
-        <v>0.520833</v>
+        <v>0.521212</v>
       </c>
       <c r="H13" t="n">
-        <v>0.530587</v>
+        <v>0.536829</v>
       </c>
       <c r="I13" t="n">
-        <v>0.525665</v>
+        <v>0.528905</v>
       </c>
       <c r="J13" t="n">
-        <v>0.25075</v>
+        <v>0.250561</v>
       </c>
       <c r="K13" t="n">
-        <v>0.526549</v>
+        <v>0.530973</v>
       </c>
       <c r="L13" t="n">
-        <v>0.53125</v>
+        <v>0.535714</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5288890000000001</v>
+        <v>0.5333329999999999</v>
       </c>
       <c r="N13" t="n">
         <v>0.2</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_17.txt</t>
+          <t>_2_3_3_3_1_1790732718_18.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1793,42 +1793,42 @@
         <v>0.1</v>
       </c>
       <c r="B14" t="n">
-        <v>0.244619</v>
+        <v>0.248882</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1790732668</v>
+        <v>1790732718</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="F14" t="n">
         <v>200000</v>
       </c>
       <c r="G14" t="n">
-        <v>0.539204</v>
+        <v>0.522103</v>
       </c>
       <c r="H14" t="n">
-        <v>0.558052</v>
+        <v>0.5455680000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.548466</v>
+        <v>0.533578</v>
       </c>
       <c r="J14" t="n">
-        <v>0.252509</v>
+        <v>0.250777</v>
       </c>
       <c r="K14" t="n">
-        <v>0.565217</v>
+        <v>0.524017</v>
       </c>
       <c r="L14" t="n">
-        <v>0.522321</v>
+        <v>0.535714</v>
       </c>
       <c r="M14" t="n">
-        <v>0.542923</v>
+        <v>0.529801</v>
       </c>
       <c r="N14" t="n">
         <v>0.2</v>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_4.txt</t>
+          <t>_2_3_3_3_1_1790732718_5.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z14" t="n">
         <v>9</v>
       </c>
       <c r="AA14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -1894,42 +1894,42 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.249249</v>
+        <v>0.245094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1790732718</v>
+        <v>1790732668</v>
       </c>
       <c r="E15" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
         <v>200000</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5254450000000001</v>
+        <v>0.546498</v>
       </c>
       <c r="H15" t="n">
-        <v>0.515606</v>
+        <v>0.594257</v>
       </c>
       <c r="I15" t="n">
-        <v>0.520479</v>
+        <v>0.5693780000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.251666</v>
+        <v>0.251513</v>
       </c>
       <c r="K15" t="n">
-        <v>0.521127</v>
+        <v>0.590909</v>
       </c>
       <c r="L15" t="n">
-        <v>0.495536</v>
+        <v>0.580357</v>
       </c>
       <c r="M15" t="n">
-        <v>0.508009</v>
+        <v>0.5855860000000001</v>
       </c>
       <c r="N15" t="n">
         <v>0.2</v>
@@ -1965,23 +1965,23 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_4.txt</t>
+          <t>_2_9_1_1790732668_3.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z15" t="n">
         <v>9</v>
       </c>
       <c r="AA15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -1995,7 +1995,7 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.248571</v>
+        <v>0.248838</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2012,25 +2012,25 @@
         <v>200000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.514673</v>
+        <v>0.516939</v>
       </c>
       <c r="H16" t="n">
-        <v>0.569288</v>
+        <v>0.514357</v>
       </c>
       <c r="I16" t="n">
-        <v>0.540605</v>
+        <v>0.515645</v>
       </c>
       <c r="J16" t="n">
-        <v>0.251129</v>
+        <v>0.25083</v>
       </c>
       <c r="K16" t="n">
-        <v>0.529412</v>
+        <v>0.5333329999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5625</v>
+        <v>0.535714</v>
       </c>
       <c r="M16" t="n">
-        <v>0.545455</v>
+        <v>0.534521</v>
       </c>
       <c r="N16" t="n">
         <v>0.2</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_13.txt</t>
+          <t>_2_3_3_3_1_1790732718_16.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2096,42 +2096,42 @@
         <v>0.1</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2491</v>
+        <v>0.241236</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1790732718</v>
+        <v>1790732668</v>
       </c>
       <c r="E17" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
         <v>200000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.523212</v>
+        <v>0.569214</v>
       </c>
       <c r="H17" t="n">
-        <v>0.520599</v>
+        <v>0.641698</v>
       </c>
       <c r="I17" t="n">
-        <v>0.521902</v>
+        <v>0.603286</v>
       </c>
       <c r="J17" t="n">
-        <v>0.250941</v>
+        <v>0.250668</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5183489999999999</v>
+        <v>0.59375</v>
       </c>
       <c r="L17" t="n">
-        <v>0.504464</v>
+        <v>0.59375</v>
       </c>
       <c r="M17" t="n">
-        <v>0.511312</v>
+        <v>0.59375</v>
       </c>
       <c r="N17" t="n">
         <v>0.2</v>
@@ -2167,23 +2167,23 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_14.txt</t>
+          <t>_2_9_1_1790732668_9.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z17" t="n">
         <v>9</v>
       </c>
       <c r="AA17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2197,42 +2197,42 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.248876</v>
+        <v>0.244979</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1790732718</v>
+        <v>1790732668</v>
       </c>
       <c r="E18" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="F18" t="n">
         <v>200000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.519065</v>
+        <v>0.543253</v>
       </c>
       <c r="H18" t="n">
-        <v>0.526841</v>
+        <v>0.588015</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5229240000000001</v>
+        <v>0.564748</v>
       </c>
       <c r="J18" t="n">
-        <v>0.250681</v>
+        <v>0.252362</v>
       </c>
       <c r="K18" t="n">
-        <v>0.52</v>
+        <v>0.584906</v>
       </c>
       <c r="L18" t="n">
-        <v>0.522321</v>
+        <v>0.553571</v>
       </c>
       <c r="M18" t="n">
-        <v>0.521158</v>
+        <v>0.568807</v>
       </c>
       <c r="N18" t="n">
         <v>0.2</v>
@@ -2268,23 +2268,23 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_12.txt</t>
+          <t>_2_9_1_1790732668_15.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z18" t="n">
         <v>9</v>
       </c>
       <c r="AA18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2298,7 +2298,7 @@
         <v>0.1</v>
       </c>
       <c r="B19" t="n">
-        <v>0.245939</v>
+        <v>0.242857</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2315,25 +2315,25 @@
         <v>200000</v>
       </c>
       <c r="G19" t="n">
-        <v>0.561547</v>
+        <v>0.545767</v>
       </c>
       <c r="H19" t="n">
-        <v>0.598002</v>
+        <v>0.595506</v>
       </c>
       <c r="I19" t="n">
-        <v>0.579202</v>
+        <v>0.5695519999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.251799</v>
+        <v>0.251505</v>
       </c>
       <c r="K19" t="n">
-        <v>0.59633</v>
+        <v>0.570776</v>
       </c>
       <c r="L19" t="n">
-        <v>0.580357</v>
+        <v>0.558036</v>
       </c>
       <c r="M19" t="n">
-        <v>0.588235</v>
+        <v>0.564334</v>
       </c>
       <c r="N19" t="n">
         <v>0.2</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_1.txt</t>
+          <t>_2_9_1_1790732668_10.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2399,7 +2399,7 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.248894</v>
+        <v>0.248754</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2416,25 +2416,25 @@
         <v>200000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.518605</v>
+        <v>0.515643</v>
       </c>
       <c r="H20" t="n">
-        <v>0.556804</v>
+        <v>0.555556</v>
       </c>
       <c r="I20" t="n">
-        <v>0.537026</v>
+        <v>0.534856</v>
       </c>
       <c r="J20" t="n">
-        <v>0.25046</v>
+        <v>0.250736</v>
       </c>
       <c r="K20" t="n">
-        <v>0.534188</v>
+        <v>0.536481</v>
       </c>
       <c r="L20" t="n">
         <v>0.558036</v>
       </c>
       <c r="M20" t="n">
-        <v>0.545852</v>
+        <v>0.547046</v>
       </c>
       <c r="N20" t="n">
         <v>0.2</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_19.txt</t>
+          <t>_2_3_3_3_1_1790732718_6.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2500,42 +2500,42 @@
         <v>0.1</v>
       </c>
       <c r="B21" t="n">
-        <v>0.248754</v>
+        <v>0.246358</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1790732718</v>
+        <v>1790732668</v>
       </c>
       <c r="E21" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
         <v>200000</v>
       </c>
       <c r="G21" t="n">
-        <v>0.515643</v>
+        <v>0.534739</v>
       </c>
       <c r="H21" t="n">
-        <v>0.555556</v>
+        <v>0.538077</v>
       </c>
       <c r="I21" t="n">
-        <v>0.534856</v>
+        <v>0.536403</v>
       </c>
       <c r="J21" t="n">
-        <v>0.250736</v>
+        <v>0.251238</v>
       </c>
       <c r="K21" t="n">
-        <v>0.536481</v>
+        <v>0.577982</v>
       </c>
       <c r="L21" t="n">
-        <v>0.558036</v>
+        <v>0.5625</v>
       </c>
       <c r="M21" t="n">
-        <v>0.547046</v>
+        <v>0.570136</v>
       </c>
       <c r="N21" t="n">
         <v>0.2</v>
@@ -2571,23 +2571,23 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_6.txt</t>
+          <t>_2_9_1_1790732668_11.txt</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z21" t="n">
         <v>9</v>
       </c>
       <c r="AA21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2601,42 +2601,42 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.245845</v>
+        <v>0.248876</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1790732668</v>
+        <v>1790732718</v>
       </c>
       <c r="E22" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="F22" t="n">
         <v>200000</v>
       </c>
       <c r="G22" t="n">
-        <v>0.545561</v>
+        <v>0.519065</v>
       </c>
       <c r="H22" t="n">
-        <v>0.583021</v>
+        <v>0.526841</v>
       </c>
       <c r="I22" t="n">
-        <v>0.563669</v>
+        <v>0.5229240000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.25183</v>
+        <v>0.250681</v>
       </c>
       <c r="K22" t="n">
-        <v>0.599119</v>
+        <v>0.52</v>
       </c>
       <c r="L22" t="n">
-        <v>0.607143</v>
+        <v>0.522321</v>
       </c>
       <c r="M22" t="n">
-        <v>0.603104</v>
+        <v>0.521158</v>
       </c>
       <c r="N22" t="n">
         <v>0.2</v>
@@ -2672,23 +2672,23 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_2.txt</t>
+          <t>_2_3_3_3_1_1790732718_12.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z22" t="n">
         <v>9</v>
       </c>
       <c r="AA22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -2702,7 +2702,7 @@
         <v>0.1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.244084</v>
+        <v>0.244246</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2719,25 +2719,25 @@
         <v>200000</v>
       </c>
       <c r="G23" t="n">
-        <v>0.545455</v>
+        <v>0.54505</v>
       </c>
       <c r="H23" t="n">
-        <v>0.606742</v>
+        <v>0.611735</v>
       </c>
       <c r="I23" t="n">
-        <v>0.574468</v>
+        <v>0.576471</v>
       </c>
       <c r="J23" t="n">
-        <v>0.251388</v>
+        <v>0.251629</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5911110000000001</v>
+        <v>0.586667</v>
       </c>
       <c r="L23" t="n">
-        <v>0.59375</v>
+        <v>0.589286</v>
       </c>
       <c r="M23" t="n">
-        <v>0.592428</v>
+        <v>0.587973</v>
       </c>
       <c r="N23" t="n">
         <v>0.2</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_14.txt</t>
+          <t>_2_9_1_1790732668_0.txt</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2803,7 +2803,7 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.244979</v>
+        <v>0.245845</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2820,25 +2820,25 @@
         <v>200000</v>
       </c>
       <c r="G24" t="n">
-        <v>0.543253</v>
+        <v>0.545561</v>
       </c>
       <c r="H24" t="n">
-        <v>0.588015</v>
+        <v>0.583021</v>
       </c>
       <c r="I24" t="n">
-        <v>0.564748</v>
+        <v>0.563669</v>
       </c>
       <c r="J24" t="n">
-        <v>0.252362</v>
+        <v>0.25183</v>
       </c>
       <c r="K24" t="n">
-        <v>0.584906</v>
+        <v>0.599119</v>
       </c>
       <c r="L24" t="n">
-        <v>0.553571</v>
+        <v>0.607143</v>
       </c>
       <c r="M24" t="n">
-        <v>0.568807</v>
+        <v>0.603104</v>
       </c>
       <c r="N24" t="n">
         <v>0.2</v>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_15.txt</t>
+          <t>_2_9_1_1790732668_2.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2904,7 +2904,7 @@
         <v>0.1</v>
       </c>
       <c r="B25" t="n">
-        <v>0.240946</v>
+        <v>0.241644</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2921,25 +2921,25 @@
         <v>200000</v>
       </c>
       <c r="G25" t="n">
-        <v>0.557032</v>
+        <v>0.572549</v>
       </c>
       <c r="H25" t="n">
-        <v>0.627965</v>
+        <v>0.546816</v>
       </c>
       <c r="I25" t="n">
-        <v>0.590376</v>
+        <v>0.559387</v>
       </c>
       <c r="J25" t="n">
-        <v>0.250354</v>
+        <v>0.251533</v>
       </c>
       <c r="K25" t="n">
-        <v>0.59276</v>
+        <v>0.564767</v>
       </c>
       <c r="L25" t="n">
-        <v>0.584821</v>
+        <v>0.486607</v>
       </c>
       <c r="M25" t="n">
-        <v>0.588764</v>
+        <v>0.522782</v>
       </c>
       <c r="N25" t="n">
         <v>0.2</v>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_16.txt</t>
+          <t>_2_9_1_1790732668_7.txt</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3005,7 +3005,7 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.245026</v>
+        <v>0.246502</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3022,25 +3022,25 @@
         <v>200000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.551208</v>
+        <v>0.547859</v>
       </c>
       <c r="H26" t="n">
-        <v>0.598002</v>
+        <v>0.543071</v>
       </c>
       <c r="I26" t="n">
-        <v>0.573653</v>
+        <v>0.545455</v>
       </c>
       <c r="J26" t="n">
-        <v>0.251791</v>
+        <v>0.251914</v>
       </c>
       <c r="K26" t="n">
-        <v>0.587156</v>
+        <v>0.56338</v>
       </c>
       <c r="L26" t="n">
-        <v>0.571429</v>
+        <v>0.535714</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5791849999999999</v>
+        <v>0.549199</v>
       </c>
       <c r="N26" t="n">
         <v>0.2</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_12.txt</t>
+          <t>_2_9_1_1790732668_13.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3106,42 +3106,42 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.248869</v>
+        <v>0.245939</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1790732718</v>
+        <v>1790732668</v>
       </c>
       <c r="E27" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="F27" t="n">
         <v>200000</v>
       </c>
       <c r="G27" t="n">
-        <v>0.524089</v>
+        <v>0.561547</v>
       </c>
       <c r="H27" t="n">
-        <v>0.556804</v>
+        <v>0.598002</v>
       </c>
       <c r="I27" t="n">
-        <v>0.539952</v>
+        <v>0.579202</v>
       </c>
       <c r="J27" t="n">
-        <v>0.250745</v>
+        <v>0.251799</v>
       </c>
       <c r="K27" t="n">
-        <v>0.528139</v>
+        <v>0.59633</v>
       </c>
       <c r="L27" t="n">
-        <v>0.544643</v>
+        <v>0.580357</v>
       </c>
       <c r="M27" t="n">
-        <v>0.536264</v>
+        <v>0.588235</v>
       </c>
       <c r="N27" t="n">
         <v>0.2</v>
@@ -3177,23 +3177,23 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_3.txt</t>
+          <t>_2_9_1_1790732668_1.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z27" t="n">
         <v>9</v>
       </c>
       <c r="AA27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3207,7 +3207,7 @@
         <v>0.1</v>
       </c>
       <c r="B28" t="n">
-        <v>0.248859</v>
+        <v>0.249119</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3224,25 +3224,25 @@
         <v>200000</v>
       </c>
       <c r="G28" t="n">
-        <v>0.521028</v>
+        <v>0.521793</v>
       </c>
       <c r="H28" t="n">
-        <v>0.556804</v>
+        <v>0.523096</v>
       </c>
       <c r="I28" t="n">
-        <v>0.538322</v>
+        <v>0.522444</v>
       </c>
       <c r="J28" t="n">
-        <v>0.250467</v>
+        <v>0.251142</v>
       </c>
       <c r="K28" t="n">
-        <v>0.536797</v>
+        <v>0.5183489999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>0.553571</v>
+        <v>0.504464</v>
       </c>
       <c r="M28" t="n">
-        <v>0.545055</v>
+        <v>0.511312</v>
       </c>
       <c r="N28" t="n">
         <v>0.2</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_7.txt</t>
+          <t>_2_3_3_3_1_1790732718_2.txt</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3308,7 +3308,7 @@
         <v>0.1</v>
       </c>
       <c r="B29" t="n">
-        <v>0.241236</v>
+        <v>0.244619</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3325,25 +3325,25 @@
         <v>200000</v>
       </c>
       <c r="G29" t="n">
-        <v>0.569214</v>
+        <v>0.539204</v>
       </c>
       <c r="H29" t="n">
-        <v>0.641698</v>
+        <v>0.558052</v>
       </c>
       <c r="I29" t="n">
-        <v>0.603286</v>
+        <v>0.548466</v>
       </c>
       <c r="J29" t="n">
-        <v>0.250668</v>
+        <v>0.252509</v>
       </c>
       <c r="K29" t="n">
-        <v>0.59375</v>
+        <v>0.565217</v>
       </c>
       <c r="L29" t="n">
-        <v>0.59375</v>
+        <v>0.522321</v>
       </c>
       <c r="M29" t="n">
-        <v>0.59375</v>
+        <v>0.542923</v>
       </c>
       <c r="N29" t="n">
         <v>0.2</v>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_9.txt</t>
+          <t>_2_9_1_1790732668_4.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3409,42 +3409,42 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.242857</v>
+        <v>0.248571</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1790732668</v>
+        <v>1790732718</v>
       </c>
       <c r="E30" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="F30" t="n">
         <v>200000</v>
       </c>
       <c r="G30" t="n">
-        <v>0.545767</v>
+        <v>0.514673</v>
       </c>
       <c r="H30" t="n">
-        <v>0.595506</v>
+        <v>0.569288</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5695519999999999</v>
+        <v>0.540605</v>
       </c>
       <c r="J30" t="n">
-        <v>0.251505</v>
+        <v>0.251129</v>
       </c>
       <c r="K30" t="n">
-        <v>0.570776</v>
+        <v>0.529412</v>
       </c>
       <c r="L30" t="n">
-        <v>0.558036</v>
+        <v>0.5625</v>
       </c>
       <c r="M30" t="n">
-        <v>0.564334</v>
+        <v>0.545455</v>
       </c>
       <c r="N30" t="n">
         <v>0.2</v>
@@ -3480,23 +3480,23 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_10.txt</t>
+          <t>_2_3_3_3_1_1790732718_13.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z30" t="n">
         <v>9</v>
       </c>
       <c r="AA30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3510,7 +3510,7 @@
         <v>0.1</v>
       </c>
       <c r="B31" t="n">
-        <v>0.248838</v>
+        <v>0.248894</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3527,25 +3527,25 @@
         <v>200000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.516939</v>
+        <v>0.518605</v>
       </c>
       <c r="H31" t="n">
-        <v>0.514357</v>
+        <v>0.556804</v>
       </c>
       <c r="I31" t="n">
-        <v>0.515645</v>
+        <v>0.537026</v>
       </c>
       <c r="J31" t="n">
-        <v>0.25083</v>
+        <v>0.25046</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5333329999999999</v>
+        <v>0.534188</v>
       </c>
       <c r="L31" t="n">
-        <v>0.535714</v>
+        <v>0.558036</v>
       </c>
       <c r="M31" t="n">
-        <v>0.534521</v>
+        <v>0.545852</v>
       </c>
       <c r="N31" t="n">
         <v>0.2</v>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_16.txt</t>
+          <t>_2_3_3_3_1_1790732718_19.txt</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3611,7 +3611,7 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.249095</v>
+        <v>0.248961</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3628,25 +3628,25 @@
         <v>200000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.527778</v>
+        <v>0.521059</v>
       </c>
       <c r="H32" t="n">
-        <v>0.498127</v>
+        <v>0.540574</v>
       </c>
       <c r="I32" t="n">
-        <v>0.512524</v>
+        <v>0.530637</v>
       </c>
       <c r="J32" t="n">
-        <v>0.251288</v>
+        <v>0.250771</v>
       </c>
       <c r="K32" t="n">
-        <v>0.526829</v>
+        <v>0.526087</v>
       </c>
       <c r="L32" t="n">
-        <v>0.482143</v>
+        <v>0.540179</v>
       </c>
       <c r="M32" t="n">
-        <v>0.5034960000000001</v>
+        <v>0.53304</v>
       </c>
       <c r="N32" t="n">
         <v>0.2</v>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_15.txt</t>
+          <t>_2_3_3_3_1_1790732718_10.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3712,7 +3712,7 @@
         <v>0.1</v>
       </c>
       <c r="B33" t="n">
-        <v>0.24884</v>
+        <v>0.249236</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3729,25 +3729,25 @@
         <v>200000</v>
       </c>
       <c r="G33" t="n">
-        <v>0.51559</v>
+        <v>0.5276</v>
       </c>
       <c r="H33" t="n">
-        <v>0.578027</v>
+        <v>0.513109</v>
       </c>
       <c r="I33" t="n">
-        <v>0.545026</v>
+        <v>0.520253</v>
       </c>
       <c r="J33" t="n">
-        <v>0.250415</v>
+        <v>0.251668</v>
       </c>
       <c r="K33" t="n">
-        <v>0.538776</v>
+        <v>0.521127</v>
       </c>
       <c r="L33" t="n">
-        <v>0.589286</v>
+        <v>0.495536</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5629</v>
+        <v>0.508009</v>
       </c>
       <c r="N33" t="n">
         <v>0.2</v>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_0.txt</t>
+          <t>_2_3_3_3_1_1790732718_8.txt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3914,7 +3914,7 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.249236</v>
+        <v>0.248893</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3931,25 +3931,25 @@
         <v>200000</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5276</v>
+        <v>0.520833</v>
       </c>
       <c r="H35" t="n">
-        <v>0.513109</v>
+        <v>0.530587</v>
       </c>
       <c r="I35" t="n">
-        <v>0.520253</v>
+        <v>0.525665</v>
       </c>
       <c r="J35" t="n">
-        <v>0.251668</v>
+        <v>0.25075</v>
       </c>
       <c r="K35" t="n">
-        <v>0.521127</v>
+        <v>0.526549</v>
       </c>
       <c r="L35" t="n">
-        <v>0.495536</v>
+        <v>0.53125</v>
       </c>
       <c r="M35" t="n">
-        <v>0.508009</v>
+        <v>0.5288890000000001</v>
       </c>
       <c r="N35" t="n">
         <v>0.2</v>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_8.txt</t>
+          <t>_2_3_3_3_1_1790732718_17.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4015,42 +4015,42 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.246502</v>
+        <v>0.24884</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1790732668</v>
+        <v>1790732718</v>
       </c>
       <c r="E36" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="F36" t="n">
         <v>200000</v>
       </c>
       <c r="G36" t="n">
-        <v>0.547859</v>
+        <v>0.51559</v>
       </c>
       <c r="H36" t="n">
-        <v>0.543071</v>
+        <v>0.578027</v>
       </c>
       <c r="I36" t="n">
-        <v>0.545455</v>
+        <v>0.545026</v>
       </c>
       <c r="J36" t="n">
-        <v>0.251914</v>
+        <v>0.250415</v>
       </c>
       <c r="K36" t="n">
-        <v>0.56338</v>
+        <v>0.538776</v>
       </c>
       <c r="L36" t="n">
-        <v>0.535714</v>
+        <v>0.589286</v>
       </c>
       <c r="M36" t="n">
-        <v>0.549199</v>
+        <v>0.5629</v>
       </c>
       <c r="N36" t="n">
         <v>0.2</v>
@@ -4086,23 +4086,23 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_13.txt</t>
+          <t>_2_3_3_3_1_1790732718_0.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z36" t="n">
         <v>9</v>
       </c>
       <c r="AA36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4116,42 +4116,42 @@
         <v>0.1</v>
       </c>
       <c r="B37" t="n">
-        <v>0.244649</v>
+        <v>0.249095</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1790732668</v>
+        <v>1790732718</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="F37" t="n">
         <v>200000</v>
       </c>
       <c r="G37" t="n">
-        <v>0.549887</v>
+        <v>0.527778</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6054929999999999</v>
+        <v>0.498127</v>
       </c>
       <c r="I37" t="n">
-        <v>0.576352</v>
+        <v>0.512524</v>
       </c>
       <c r="J37" t="n">
-        <v>0.252144</v>
+        <v>0.251288</v>
       </c>
       <c r="K37" t="n">
-        <v>0.589041</v>
+        <v>0.526829</v>
       </c>
       <c r="L37" t="n">
-        <v>0.575893</v>
+        <v>0.482143</v>
       </c>
       <c r="M37" t="n">
-        <v>0.582393</v>
+        <v>0.5034960000000001</v>
       </c>
       <c r="N37" t="n">
         <v>0.2</v>
@@ -4187,23 +4187,23 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_19.txt</t>
+          <t>_2_3_3_3_1_1790732718_15.txt</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z37" t="n">
         <v>9</v>
       </c>
       <c r="AA37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4217,42 +4217,42 @@
         <v>0.1</v>
       </c>
       <c r="B38" t="n">
-        <v>0.248981</v>
+        <v>0.244649</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1790732718</v>
+        <v>1790732668</v>
       </c>
       <c r="E38" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="F38" t="n">
         <v>200000</v>
       </c>
       <c r="G38" t="n">
-        <v>0.521212</v>
+        <v>0.549887</v>
       </c>
       <c r="H38" t="n">
-        <v>0.536829</v>
+        <v>0.6054929999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>0.528905</v>
+        <v>0.576352</v>
       </c>
       <c r="J38" t="n">
-        <v>0.250561</v>
+        <v>0.252144</v>
       </c>
       <c r="K38" t="n">
-        <v>0.530973</v>
+        <v>0.589041</v>
       </c>
       <c r="L38" t="n">
-        <v>0.535714</v>
+        <v>0.575893</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5333329999999999</v>
+        <v>0.582393</v>
       </c>
       <c r="N38" t="n">
         <v>0.2</v>
@@ -4288,23 +4288,23 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_18.txt</t>
+          <t>_2_9_1_1790732668_19.txt</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z38" t="n">
         <v>9</v>
       </c>
       <c r="AA38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4318,42 +4318,42 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.245522</v>
+        <v>0.248859</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1790732668</v>
+        <v>1790732718</v>
       </c>
       <c r="E39" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="F39" t="n">
         <v>200000</v>
       </c>
       <c r="G39" t="n">
-        <v>0.553653</v>
+        <v>0.521028</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6054929999999999</v>
+        <v>0.556804</v>
       </c>
       <c r="I39" t="n">
-        <v>0.578414</v>
+        <v>0.538322</v>
       </c>
       <c r="J39" t="n">
-        <v>0.252012</v>
+        <v>0.250467</v>
       </c>
       <c r="K39" t="n">
-        <v>0.591928</v>
+        <v>0.536797</v>
       </c>
       <c r="L39" t="n">
-        <v>0.589286</v>
+        <v>0.553571</v>
       </c>
       <c r="M39" t="n">
-        <v>0.590604</v>
+        <v>0.545055</v>
       </c>
       <c r="N39" t="n">
         <v>0.2</v>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_6.txt</t>
+          <t>_2_3_3_3_1_1790732718_7.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z39" t="n">
         <v>9</v>
       </c>
       <c r="AA39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4419,7 +4419,7 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.244246</v>
+        <v>0.243187</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4436,25 +4436,25 @@
         <v>200000</v>
       </c>
       <c r="G40" t="n">
-        <v>0.54505</v>
+        <v>0.54535</v>
       </c>
       <c r="H40" t="n">
-        <v>0.611735</v>
+        <v>0.593009</v>
       </c>
       <c r="I40" t="n">
-        <v>0.576471</v>
+        <v>0.568182</v>
       </c>
       <c r="J40" t="n">
-        <v>0.251629</v>
+        <v>0.252278</v>
       </c>
       <c r="K40" t="n">
-        <v>0.586667</v>
+        <v>0.579186</v>
       </c>
       <c r="L40" t="n">
-        <v>0.589286</v>
+        <v>0.571429</v>
       </c>
       <c r="M40" t="n">
-        <v>0.587973</v>
+        <v>0.575281</v>
       </c>
       <c r="N40" t="n">
         <v>0.2</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_2_9_1_1790732668_0.txt</t>
+          <t>_2_9_1_1790732668_17.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4520,7 +4520,7 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.248961</v>
+        <v>0.249249</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4537,25 +4537,25 @@
         <v>200000</v>
       </c>
       <c r="G41" t="n">
-        <v>0.521059</v>
+        <v>0.5254450000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>0.540574</v>
+        <v>0.515606</v>
       </c>
       <c r="I41" t="n">
-        <v>0.530637</v>
+        <v>0.520479</v>
       </c>
       <c r="J41" t="n">
-        <v>0.250771</v>
+        <v>0.251666</v>
       </c>
       <c r="K41" t="n">
-        <v>0.526087</v>
+        <v>0.521127</v>
       </c>
       <c r="L41" t="n">
-        <v>0.540179</v>
+        <v>0.495536</v>
       </c>
       <c r="M41" t="n">
-        <v>0.53304</v>
+        <v>0.508009</v>
       </c>
       <c r="N41" t="n">
         <v>0.2</v>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790732718_10.txt</t>
+          <t>_2_3_3_3_1_1790732718_4.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4682,7 +4682,7 @@
         <v>0.52700795</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01740024170574708</v>
+        <v>0.01740024170574709</v>
       </c>
       <c r="D2" t="n">
         <v>0.5629</v>
@@ -4710,7 +4710,7 @@
         <v>0.5762311999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01983028597771335</v>
+        <v>0.01983028597771336</v>
       </c>
       <c r="D3" t="n">
         <v>0.603104</v>
